--- a/Excel/EquipRedConfig.xlsx
+++ b/Excel/EquipRedConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WrittenLegend\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="27">
   <si>
     <t>#</t>
   </si>
@@ -1065,8 +1070,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:J63"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
+  <dimension ref="C1:J76"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
     <col min="4" max="6" width="16.25" style="1" customWidth="1"/>
@@ -1076,12 +1081,12 @@
     <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:10">
+    <row r="1" customHeight="1" spans="3:10">
       <c r="J1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" ht="13.5" spans="3:10">
+    <row r="3" customHeight="1" spans="3:10">
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1104,7 +1109,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" ht="13.5" spans="3:10">
+    <row r="4" customHeight="1" spans="3:10">
       <c r="C4" s="2" t="s">
         <v>8</v>
       </c>
@@ -1127,7 +1132,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" ht="13.5" spans="3:10">
+    <row r="5" customHeight="1" spans="3:10">
       <c r="C5" s="2" t="s">
         <v>9</v>
       </c>
@@ -1150,7 +1155,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="3:10">
+    <row r="6" customHeight="1" spans="3:10">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1176,7 +1181,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="3:10">
+    <row r="7" customHeight="1" spans="3:10">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1202,7 +1207,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="3:10">
+    <row r="8" customHeight="1" spans="3:10">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1228,7 +1233,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="3:10">
+    <row r="9" customHeight="1" spans="3:10">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1254,7 +1259,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="3:10">
+    <row r="10" customHeight="1" spans="3:10">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1280,7 +1285,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="3:10">
+    <row r="11" customHeight="1" spans="3:10">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1306,7 +1311,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="3:10">
+    <row r="12" customHeight="1" spans="3:10">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -1332,7 +1337,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="3:10">
+    <row r="13" customHeight="1" spans="3:10">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -1358,7 +1363,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="3:10">
+    <row r="14" customHeight="1" spans="3:10">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -1384,7 +1389,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="3:10">
+    <row r="16" customHeight="1" spans="3:10">
       <c r="C16" s="1">
         <v>10</v>
       </c>
@@ -1410,7 +1415,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="3:10">
+    <row r="17" customHeight="1" spans="3:10">
       <c r="C17" s="1">
         <v>11</v>
       </c>
@@ -1436,7 +1441,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="3:10">
+    <row r="18" customHeight="1" spans="3:10">
       <c r="C18" s="1">
         <v>12</v>
       </c>
@@ -1462,7 +1467,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="3:10">
+    <row r="19" customHeight="1" spans="3:10">
       <c r="C19" s="1">
         <v>13</v>
       </c>
@@ -1488,7 +1493,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="3:10">
+    <row r="20" customHeight="1" spans="3:10">
       <c r="C20" s="1">
         <v>14</v>
       </c>
@@ -1514,7 +1519,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="3:10">
+    <row r="21" customHeight="1" spans="3:10">
       <c r="C21" s="1">
         <v>15</v>
       </c>
@@ -1540,7 +1545,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="3:10">
+    <row r="22" customHeight="1" spans="3:10">
       <c r="C22" s="1">
         <v>16</v>
       </c>
@@ -1566,7 +1571,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="3:10">
+    <row r="23" customHeight="1" spans="3:10">
       <c r="C23" s="1">
         <v>17</v>
       </c>
@@ -1592,7 +1597,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="3:10">
+    <row r="24" customHeight="1" spans="3:10">
       <c r="C24" s="1">
         <v>18</v>
       </c>
@@ -1618,7 +1623,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="3:10">
+    <row r="26" customHeight="1" spans="3:10">
       <c r="C26" s="1">
         <v>19</v>
       </c>
@@ -1644,7 +1649,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="3:10">
+    <row r="27" customHeight="1" spans="3:10">
       <c r="C27" s="1">
         <v>20</v>
       </c>
@@ -1670,7 +1675,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="3:10">
+    <row r="28" customHeight="1" spans="3:10">
       <c r="C28" s="1">
         <v>21</v>
       </c>
@@ -1696,7 +1701,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="3:10">
+    <row r="29" customHeight="1" spans="3:10">
       <c r="C29" s="1">
         <v>22</v>
       </c>
@@ -1722,7 +1727,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="3:10">
+    <row r="30" customHeight="1" spans="3:10">
       <c r="C30" s="1">
         <v>23</v>
       </c>
@@ -1748,7 +1753,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="3:10">
+    <row r="31" customHeight="1" spans="3:10">
       <c r="C31" s="1">
         <v>24</v>
       </c>
@@ -1774,7 +1779,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="3:10">
+    <row r="32" customHeight="1" spans="3:10">
       <c r="C32" s="1">
         <v>25</v>
       </c>
@@ -1800,7 +1805,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="3:10">
+    <row r="33" customHeight="1" spans="3:10">
       <c r="C33" s="1">
         <v>26</v>
       </c>
@@ -1826,7 +1831,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="3:10">
+    <row r="34" customHeight="1" spans="3:10">
       <c r="C34" s="1">
         <v>27</v>
       </c>
@@ -1852,7 +1857,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="3:10">
+    <row r="35" customHeight="1" spans="3:10">
       <c r="C35" s="1">
         <v>28</v>
       </c>
@@ -1878,7 +1883,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="36" spans="3:10">
+    <row r="36" customHeight="1" spans="3:10">
       <c r="C36" s="1">
         <v>29</v>
       </c>
@@ -1904,7 +1909,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="37" spans="3:10">
+    <row r="37" customHeight="1" spans="3:10">
       <c r="C37" s="1">
         <v>30</v>
       </c>
@@ -1930,7 +1935,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="3:10">
+    <row r="39" customHeight="1" spans="3:10">
       <c r="C39" s="1">
         <v>31</v>
       </c>
@@ -1956,7 +1961,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="3:10">
+    <row r="40" customHeight="1" spans="3:10">
       <c r="C40" s="1">
         <v>32</v>
       </c>
@@ -1982,7 +1987,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="41" spans="3:10">
+    <row r="41" customHeight="1" spans="3:10">
       <c r="C41" s="1">
         <v>33</v>
       </c>
@@ -2008,7 +2013,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="42" spans="3:10">
+    <row r="42" customHeight="1" spans="3:10">
       <c r="C42" s="1">
         <v>34</v>
       </c>
@@ -2034,7 +2039,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="3:10">
+    <row r="43" customHeight="1" spans="3:10">
       <c r="C43" s="1">
         <v>35</v>
       </c>
@@ -2060,7 +2065,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="44" spans="3:10">
+    <row r="44" customHeight="1" spans="3:10">
       <c r="C44" s="1">
         <v>36</v>
       </c>
@@ -2086,7 +2091,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="3:10">
+    <row r="45" customHeight="1" spans="3:10">
       <c r="C45" s="1">
         <v>37</v>
       </c>
@@ -2112,7 +2117,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="46" spans="3:10">
+    <row r="46" customHeight="1" spans="3:10">
       <c r="C46" s="1">
         <v>38</v>
       </c>
@@ -2138,7 +2143,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="3:10">
+    <row r="47" customHeight="1" spans="3:10">
       <c r="C47" s="1">
         <v>39</v>
       </c>
@@ -2164,7 +2169,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="48" spans="3:10">
+    <row r="48" customHeight="1" spans="3:10">
       <c r="C48" s="1">
         <v>40</v>
       </c>
@@ -2190,7 +2195,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="49" spans="3:10">
+    <row r="49" customHeight="1" spans="3:10">
       <c r="C49" s="1">
         <v>41</v>
       </c>
@@ -2216,7 +2221,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="50" spans="3:10">
+    <row r="50" customHeight="1" spans="3:10">
       <c r="C50" s="1">
         <v>42</v>
       </c>
@@ -2242,7 +2247,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="52" spans="3:10">
+    <row r="52" customHeight="1" spans="3:10">
       <c r="C52" s="1">
         <v>43</v>
       </c>
@@ -2268,7 +2273,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="3:10">
+    <row r="53" customHeight="1" spans="3:10">
       <c r="C53" s="1">
         <v>44</v>
       </c>
@@ -2294,7 +2299,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="54" spans="3:10">
+    <row r="54" customHeight="1" spans="3:10">
       <c r="C54" s="1">
         <v>45</v>
       </c>
@@ -2320,7 +2325,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="55" spans="3:10">
+    <row r="55" customHeight="1" spans="3:10">
       <c r="C55" s="1">
         <v>46</v>
       </c>
@@ -2346,7 +2351,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="56" spans="3:10">
+    <row r="56" customHeight="1" spans="3:10">
       <c r="C56" s="1">
         <v>47</v>
       </c>
@@ -2372,7 +2377,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="57" spans="3:10">
+    <row r="57" customHeight="1" spans="3:10">
       <c r="C57" s="1">
         <v>48</v>
       </c>
@@ -2398,7 +2403,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="58" spans="3:10">
+    <row r="58" customHeight="1" spans="3:10">
       <c r="C58" s="1">
         <v>49</v>
       </c>
@@ -2424,7 +2429,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="59" spans="3:10">
+    <row r="59" customHeight="1" spans="3:10">
       <c r="C59" s="1">
         <v>50</v>
       </c>
@@ -2450,7 +2455,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="60" spans="3:10">
+    <row r="60" customHeight="1" spans="3:10">
       <c r="C60" s="1">
         <v>51</v>
       </c>
@@ -2476,7 +2481,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="61" spans="3:10">
+    <row r="61" customHeight="1" spans="3:10">
       <c r="C61" s="1">
         <v>52</v>
       </c>
@@ -2502,7 +2507,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="62" spans="3:10">
+    <row r="62" customHeight="1" spans="3:10">
       <c r="C62" s="1">
         <v>53</v>
       </c>
@@ -2528,7 +2533,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="63" spans="3:10">
+    <row r="63" customHeight="1" spans="3:10">
       <c r="C63" s="1">
         <v>54</v>
       </c>
@@ -2551,6 +2556,318 @@
         <v>80</v>
       </c>
       <c r="J63" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="3:10">
+      <c r="C65" s="1">
+        <v>55</v>
+      </c>
+      <c r="D65" s="1">
+        <v>1</v>
+      </c>
+      <c r="E65" s="1">
+        <v>11</v>
+      </c>
+      <c r="F65" s="1">
+        <v>2</v>
+      </c>
+      <c r="G65" s="1">
+        <v>2004</v>
+      </c>
+      <c r="H65" s="1">
+        <v>160</v>
+      </c>
+      <c r="I65" s="1">
+        <v>160</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="3:10">
+      <c r="C66" s="1">
+        <v>56</v>
+      </c>
+      <c r="D66" s="1">
+        <v>1</v>
+      </c>
+      <c r="E66" s="1">
+        <v>11</v>
+      </c>
+      <c r="F66" s="1">
+        <v>6</v>
+      </c>
+      <c r="G66" s="1">
+        <v>2007</v>
+      </c>
+      <c r="H66" s="1">
+        <v>240</v>
+      </c>
+      <c r="I66" s="1">
+        <v>240</v>
+      </c>
+      <c r="J66" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="3:10">
+      <c r="C67" s="1">
+        <v>57</v>
+      </c>
+      <c r="D67" s="1">
+        <v>1</v>
+      </c>
+      <c r="E67" s="1">
+        <v>11</v>
+      </c>
+      <c r="F67" s="1">
+        <v>8</v>
+      </c>
+      <c r="G67" s="1">
+        <v>2001</v>
+      </c>
+      <c r="H67" s="1">
+        <v>320</v>
+      </c>
+      <c r="I67" s="1">
+        <v>320</v>
+      </c>
+      <c r="J67" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="3:10">
+      <c r="C68" s="1">
+        <v>58</v>
+      </c>
+      <c r="D68" s="1">
+        <v>1</v>
+      </c>
+      <c r="E68" s="1">
+        <v>11</v>
+      </c>
+      <c r="F68" s="1">
+        <v>10</v>
+      </c>
+      <c r="G68" s="1">
+        <v>2013</v>
+      </c>
+      <c r="H68" s="1">
+        <v>160</v>
+      </c>
+      <c r="I68" s="1">
+        <v>160</v>
+      </c>
+      <c r="J68" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="69" customHeight="1" spans="3:10">
+      <c r="C69" s="1">
+        <v>59</v>
+      </c>
+      <c r="D69" s="1">
+        <v>2</v>
+      </c>
+      <c r="E69" s="1">
+        <v>11</v>
+      </c>
+      <c r="F69" s="1">
+        <v>2</v>
+      </c>
+      <c r="G69" s="1">
+        <v>2005</v>
+      </c>
+      <c r="H69" s="1">
+        <v>160</v>
+      </c>
+      <c r="I69" s="1">
+        <v>160</v>
+      </c>
+      <c r="J69" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70" customHeight="1" spans="3:10">
+      <c r="C70" s="1">
+        <v>60</v>
+      </c>
+      <c r="D70" s="1">
+        <v>2</v>
+      </c>
+      <c r="E70" s="1">
+        <v>11</v>
+      </c>
+      <c r="F70" s="1">
+        <v>6</v>
+      </c>
+      <c r="G70" s="1">
+        <v>2008</v>
+      </c>
+      <c r="H70" s="1">
+        <v>240</v>
+      </c>
+      <c r="I70" s="1">
+        <v>240</v>
+      </c>
+      <c r="J70" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="71" customHeight="1" spans="3:10">
+      <c r="C71" s="1">
+        <v>61</v>
+      </c>
+      <c r="D71" s="1">
+        <v>2</v>
+      </c>
+      <c r="E71" s="1">
+        <v>11</v>
+      </c>
+      <c r="F71" s="1">
+        <v>8</v>
+      </c>
+      <c r="G71" s="1">
+        <v>2001</v>
+      </c>
+      <c r="H71" s="1">
+        <v>320</v>
+      </c>
+      <c r="I71" s="1">
+        <v>320</v>
+      </c>
+      <c r="J71" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="3:10">
+      <c r="C72" s="1">
+        <v>62</v>
+      </c>
+      <c r="D72" s="1">
+        <v>2</v>
+      </c>
+      <c r="E72" s="1">
+        <v>11</v>
+      </c>
+      <c r="F72" s="1">
+        <v>10</v>
+      </c>
+      <c r="G72" s="1">
+        <v>2013</v>
+      </c>
+      <c r="H72" s="1">
+        <v>160</v>
+      </c>
+      <c r="I72" s="1">
+        <v>160</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="3:10">
+      <c r="C73" s="1">
+        <v>63</v>
+      </c>
+      <c r="D73" s="1">
+        <v>3</v>
+      </c>
+      <c r="E73" s="1">
+        <v>11</v>
+      </c>
+      <c r="F73" s="1">
+        <v>2</v>
+      </c>
+      <c r="G73" s="1">
+        <v>2006</v>
+      </c>
+      <c r="H73" s="1">
+        <v>160</v>
+      </c>
+      <c r="I73" s="1">
+        <v>160</v>
+      </c>
+      <c r="J73" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="3:10">
+      <c r="C74" s="1">
+        <v>64</v>
+      </c>
+      <c r="D74" s="1">
+        <v>3</v>
+      </c>
+      <c r="E74" s="1">
+        <v>11</v>
+      </c>
+      <c r="F74" s="1">
+        <v>6</v>
+      </c>
+      <c r="G74" s="1">
+        <v>2009</v>
+      </c>
+      <c r="H74" s="1">
+        <v>240</v>
+      </c>
+      <c r="I74" s="1">
+        <v>240</v>
+      </c>
+      <c r="J74" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="3:10">
+      <c r="C75" s="1">
+        <v>65</v>
+      </c>
+      <c r="D75" s="1">
+        <v>3</v>
+      </c>
+      <c r="E75" s="1">
+        <v>11</v>
+      </c>
+      <c r="F75" s="1">
+        <v>8</v>
+      </c>
+      <c r="G75" s="1">
+        <v>2001</v>
+      </c>
+      <c r="H75" s="1">
+        <v>320</v>
+      </c>
+      <c r="I75" s="1">
+        <v>320</v>
+      </c>
+      <c r="J75" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="3:10">
+      <c r="C76" s="1">
+        <v>66</v>
+      </c>
+      <c r="D76" s="1">
+        <v>3</v>
+      </c>
+      <c r="E76" s="1">
+        <v>11</v>
+      </c>
+      <c r="F76" s="1">
+        <v>10</v>
+      </c>
+      <c r="G76" s="1">
+        <v>2013</v>
+      </c>
+      <c r="H76" s="1">
+        <v>160</v>
+      </c>
+      <c r="I76" s="1">
+        <v>160</v>
+      </c>
+      <c r="J76" s="1" t="s">
         <v>26</v>
       </c>
     </row>
